--- a/Assets/Resources/ShopData/Shop00001.xlsx
+++ b/Assets/Resources/ShopData/Shop00001.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\SangDol\Assets\Resources\ShopData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C47C5704-9752-46D5-9986-0AF8C742F687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BD2DDF5-B139-4A2C-8B89-4974AEFE48E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
@@ -390,6 +390,14 @@
       </c>
       <c r="B4">
         <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>10007</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/ShopData/Shop00001.xlsx
+++ b/Assets/Resources/ShopData/Shop00001.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\SangDol\Assets\Resources\ShopData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BD2DDF5-B139-4A2C-8B89-4974AEFE48E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5572351E-7004-4E88-B8AB-DDFE3859BD51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6420" yWindow="2700" windowWidth="19845" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
@@ -397,6 +397,14 @@
         <v>10007</v>
       </c>
       <c r="B5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>10015</v>
+      </c>
+      <c r="B6">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/ShopData/Shop00001.xlsx
+++ b/Assets/Resources/ShopData/Shop00001.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\SangDol\Assets\Resources\ShopData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5572351E-7004-4E88-B8AB-DDFE3859BD51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EF51522-75A8-4CA1-8E61-C1FFBD90AB6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6420" yWindow="2700" windowWidth="19845" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6660" yWindow="1770" windowWidth="19845" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
@@ -370,7 +370,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>10001</v>
+        <v>20008</v>
       </c>
       <c r="B2">
         <v>100</v>
@@ -378,7 +378,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>10002</v>
+        <v>20001</v>
       </c>
       <c r="B3">
         <v>100</v>
@@ -386,26 +386,10 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>10003</v>
+        <v>20009</v>
       </c>
       <c r="B4">
         <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>10007</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>10015</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
